--- a/data/trans_orig/P15D$nada-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15D$nada-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>18004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>23614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36243</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34757</t>
+          <t>35996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50471</t>
+          <t>51466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>13488</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>28953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48247</t>
+          <t>48264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26944</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48781</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71634</t>
+          <t>71216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>53,55%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10437</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>23046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42545</t>
+          <t>42555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23607</t>
+          <t>24120</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60982</t>
+          <t>61094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>25623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40138</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46445</t>
+          <t>45632</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68865</t>
+          <t>68392</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51379</t>
+          <t>50824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70627</t>
+          <t>69211</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101500</t>
+          <t>103625</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133121</t>
+          <t>132591</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33396</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21411</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43030</t>
+          <t>42277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35941</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58507</t>
+          <t>59516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>13578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>24913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34508</t>
+          <t>34056</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51744</t>
+          <t>52139</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47200</t>
+          <t>47466</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69045</t>
+          <t>67893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88143</t>
+          <t>87887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116209</t>
+          <t>115601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20548</t>
+          <t>20789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14639</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34405</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36379</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>59994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23943</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44266</t>
+          <t>44461</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65808</t>
+          <t>65485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100132</t>
+          <t>98374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>17724</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31747</t>
+          <t>31926</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97966</t>
+          <t>96561</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123313</t>
+          <t>124112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52461</t>
+          <t>52525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74201</t>
+          <t>73480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153409</t>
+          <t>156596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191511</t>
+          <t>191377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>21106</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14269</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12779</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30372</t>
+          <t>30207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>15007</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>22237</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23807</t>
+          <t>23996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23650</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38944</t>
+          <t>39260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56149</t>
+          <t>56452</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86534</t>
+          <t>86790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>58345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>87992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123666</t>
+          <t>123650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164036</t>
+          <t>164775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15486</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35227</t>
+          <t>33540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31420</t>
+          <t>31828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32712</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>59969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>146995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180372</t>
+          <t>183600</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>123411</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158211</t>
+          <t>153519</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>284897</t>
+          <t>282453</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>331661</t>
+          <t>330834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34495</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>32464</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>58627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30534</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30159</t>
+          <t>29339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28927</t>
+          <t>28871</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>33262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51190</t>
+          <t>51933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54462</t>
+          <t>54752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76607</t>
+          <t>76155</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22660</t>
+          <t>22352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>31898</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>21856</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44645</t>
+          <t>43799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20378</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28651</t>
+          <t>29820</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66724</t>
+          <t>67421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88571</t>
+          <t>88661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52194</t>
+          <t>53074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69382</t>
+          <t>68974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125803</t>
+          <t>125246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151761</t>
+          <t>152765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5638,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27312</t>
+          <t>27082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>24832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25261</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46701</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -6094,12 +6094,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>23606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43806</t>
+          <t>45093</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46040</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75327</t>
+          <t>75440</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>29343</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32494</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57522</t>
+          <t>57094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>106540</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134113</t>
+          <t>132787</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109543</t>
+          <t>109229</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>136873</t>
+          <t>136949</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>223968</t>
+          <t>224181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>264416</t>
+          <t>262007</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29600</t>
+          <t>32228</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56523</t>
+          <t>57675</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>12446</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>28620</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20544</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35408</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10922</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21241</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20624</t>
+          <t>21959</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>28802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -7119,17 +7119,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35013</t>
+          <t>37762</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>30816</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>44399</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>44630</t>
+          <t>47982</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>39353</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52244</t>
+          <t>56479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>16334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7267,32 +7267,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>17469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>32468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23974</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>32126</t>
+          <t>32615</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43513</t>
+          <t>43912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24763</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>26747</t>
+          <t>27479</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>18482</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39345</t>
+          <t>40566</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89713</t>
+          <t>98552</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76557</t>
+          <t>86736</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99692</t>
+          <t>109268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>63357</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>52660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65923</t>
+          <t>73512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146746</t>
+          <t>161908</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131452</t>
+          <t>146177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162095</t>
+          <t>178408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23995</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7723,27 +7723,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>23179</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>41645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>23543</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24886</t>
+          <t>31434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>41812</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>50919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -8144,32 +8144,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8179,32 +8179,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8214,32 +8214,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>32567</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>22793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43402</t>
+          <t>45812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30663</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50479</t>
+          <t>54038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>72884</t>
+          <t>74799</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>60438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89229</t>
+          <t>91184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27574</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>42255</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31068</t>
+          <t>32670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50434</t>
+          <t>53996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>61101</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45280</t>
+          <t>49288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71441</t>
+          <t>75739</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>132315</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103356</t>
+          <t>115598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133233</t>
+          <t>147944</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,67 +8522,67 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>107626</t>
+          <t>119388</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>96429</t>
+          <t>105374</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120146</t>
+          <t>133569</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
+          <t>51,73%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>45,66%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>57,88%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>251703</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>228309</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>272153</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>55,87%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>50,68%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>45,4%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>225384</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>203297</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>244297</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>54,8%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>49,43%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,41%</t>
         </is>
       </c>
     </row>
@@ -8600,32 +8600,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23485</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>51041</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8635,32 +8635,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8670,32 +8670,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>62913</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44150</t>
+          <t>49110</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72333</t>
+          <t>80565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
